--- a/教材資料/EnglishApp_教員用_単語文章一覧.xlsx
+++ b/教材資料/EnglishApp_教員用_単語文章一覧.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フォニックス" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'語彙一覧'!$A$1:$E$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'語彙一覧'!$A$1:$E$263</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6871,8 +6871,308 @@
         <v>19</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B252" s="5" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="inlineStr">
+        <is>
+          <t>英語</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E252" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t>国語</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B254" s="5" t="inlineStr">
+        <is>
+          <t>calligraphy</t>
+        </is>
+      </c>
+      <c r="C254" s="5" t="inlineStr">
+        <is>
+          <t>書道</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="inlineStr">
+        <is>
+          <t>social studies</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="inlineStr">
+        <is>
+          <t>社会</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B256" s="5" t="inlineStr">
+        <is>
+          <t>math</t>
+        </is>
+      </c>
+      <c r="C256" s="5" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E256" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
+        <is>
+          <t>science</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>理科</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="inlineStr">
+        <is>
+          <t>music</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>音楽</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>arts and crafts</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t>図工</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>home economics</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>家庭科</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>P.E.</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>体育</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B262" s="5" t="inlineStr">
+        <is>
+          <t>moral education</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="inlineStr">
+        <is>
+          <t>道徳</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
+        <is>
+          <t>period for integrated studies</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>総合の時間</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E251"/>
+  <autoFilter ref="A1:E263"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6883,7 +7183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7176,6 +7476,21 @@
       </c>
       <c r="C19" s="5" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>教科</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/教材資料/EnglishApp_教員用_単語文章一覧.xlsx
+++ b/教材資料/EnglishApp_教員用_単語文章一覧.xlsx
@@ -8744,12 +8744,12 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Nice! I like {music}, too.</t>
+          <t>Oh, nice! I like {science}.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>いいね！ぼくは【音楽】が好き。</t>
+          <t>いいね！ぼくは【理科】が好き。</t>
         </is>
       </c>
     </row>

--- a/教材資料/EnglishApp_教員用_単語文章一覧.xlsx
+++ b/教材資料/EnglishApp_教員用_単語文章一覧.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フォニックス" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'語彙一覧'!$A$1:$E$263</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'語彙一覧'!$A$1:$E$564</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E263"/>
+  <dimension ref="A1:E564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7171,8 +7171,7533 @@
         <v>28</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B264" s="5" t="inlineStr">
+        <is>
+          <t>baseball</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>野球</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>soccer</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>サッカー</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>バスケットボール</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>テニス</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>バレーボール</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
+        <is>
+          <t>dodgeball</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>ドッジボール</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
+        <is>
+          <t>table tennis</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>卓球</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
+        <is>
+          <t>judo</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>柔道</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B272" s="5" t="inlineStr">
+        <is>
+          <t>kendo</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="inlineStr">
+        <is>
+          <t>剣道</t>
+        </is>
+      </c>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B273" s="5" t="inlineStr">
+        <is>
+          <t>badminton</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>バドミントン</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B274" s="5" t="inlineStr">
+        <is>
+          <t>cricket</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="inlineStr">
+        <is>
+          <t>クリケット</t>
+        </is>
+      </c>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>ラグビー</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="inlineStr">
+        <is>
+          <t>sumo</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>すもう</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
+        <is>
+          <t>swimming</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>水泳</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="inlineStr">
+        <is>
+          <t>gymnastics</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="inlineStr">
+        <is>
+          <t>体操</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="inlineStr">
+        <is>
+          <t>track and field</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>陸上</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B280" s="5" t="inlineStr">
+        <is>
+          <t>skateboarding</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="inlineStr">
+        <is>
+          <t>スケートボード</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B281" s="5" t="inlineStr">
+        <is>
+          <t>skiing</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>スキー</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B282" s="5" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="inlineStr">
+        <is>
+          <t>くま</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B283" s="5" t="inlineStr">
+        <is>
+          <t>elephant</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>ぞう</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B284" s="5" t="inlineStr">
+        <is>
+          <t>tiger</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>とら</t>
+        </is>
+      </c>
+      <c r="D284" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B285" s="5" t="inlineStr">
+        <is>
+          <t>lion</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>ライオン</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B286" s="5" t="inlineStr">
+        <is>
+          <t>horse</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>うま</t>
+        </is>
+      </c>
+      <c r="D286" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>monkey</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>さる</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B288" s="5" t="inlineStr">
+        <is>
+          <t>zebra</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t>しまうま</t>
+        </is>
+      </c>
+      <c r="D288" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
+        <is>
+          <t>camel</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>らくだ</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
+        <is>
+          <t>giraffe</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>きりん</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
+        <is>
+          <t>gorilla</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>ゴリラ</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B292" s="5" t="inlineStr">
+        <is>
+          <t>deer</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>しか</t>
+        </is>
+      </c>
+      <c r="D292" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E292" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
+        <is>
+          <t>orangutan</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>オランウータン</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
+        <is>
+          <t>panda</t>
+        </is>
+      </c>
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>パンダ</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
+        <is>
+          <t>koala</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>コアラ</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
+        <is>
+          <t>fox</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>きつね</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
+        <is>
+          <t>rabbit</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>うさぎ</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
+        <is>
+          <t>mouse</t>
+        </is>
+      </c>
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>ねずみ</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B299" s="5" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t>いぬ</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B300" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="inlineStr">
+        <is>
+          <t>ねこ</t>
+        </is>
+      </c>
+      <c r="D300" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B301" s="5" t="inlineStr">
+        <is>
+          <t>frog</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>かえる</t>
+        </is>
+      </c>
+      <c r="D301" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B302" s="5" t="inlineStr">
+        <is>
+          <t>bird</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t>とり</t>
+        </is>
+      </c>
+      <c r="D302" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
+        <is>
+          <t>crocodile</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>ワニ</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
+        <is>
+          <t>snake</t>
+        </is>
+      </c>
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>へび</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="5" t="inlineStr">
+        <is>
+          <t>自然</t>
+        </is>
+      </c>
+      <c r="B305" s="5" t="inlineStr">
+        <is>
+          <t>river</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>川</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="5" t="inlineStr">
+        <is>
+          <t>自然</t>
+        </is>
+      </c>
+      <c r="B306" s="5" t="inlineStr">
+        <is>
+          <t>desert</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t>さばく</t>
+        </is>
+      </c>
+      <c r="D306" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t>自然</t>
+        </is>
+      </c>
+      <c r="B307" s="5" t="inlineStr">
+        <is>
+          <t>savanna</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>サバンナ</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="5" t="inlineStr">
+        <is>
+          <t>自然</t>
+        </is>
+      </c>
+      <c r="B308" s="5" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t>森</t>
+        </is>
+      </c>
+      <c r="D308" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="5" t="inlineStr">
+        <is>
+          <t>自然</t>
+        </is>
+      </c>
+      <c r="B309" s="5" t="inlineStr">
+        <is>
+          <t>rainforest</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>熱帯雨林</t>
+        </is>
+      </c>
+      <c r="D309" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="5" t="inlineStr">
+        <is>
+          <t>自然</t>
+        </is>
+      </c>
+      <c r="B310" s="5" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>海</t>
+        </is>
+      </c>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t>自然</t>
+        </is>
+      </c>
+      <c r="B311" s="5" t="inlineStr">
+        <is>
+          <t>lake</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>湖</t>
+        </is>
+      </c>
+      <c r="D311" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="5" t="inlineStr">
+        <is>
+          <t>自然</t>
+        </is>
+      </c>
+      <c r="B312" s="5" t="inlineStr">
+        <is>
+          <t>mountain</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>山</t>
+        </is>
+      </c>
+      <c r="D312" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>海の生き物</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>whale</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>クジラ</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="inlineStr">
+        <is>
+          <t>海の生き物</t>
+        </is>
+      </c>
+      <c r="B314" s="5" t="inlineStr">
+        <is>
+          <t>shark</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>サメ</t>
+        </is>
+      </c>
+      <c r="D314" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t>海の生き物</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
+        <is>
+          <t>dolphin</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>イルカ</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="5" t="inlineStr">
+        <is>
+          <t>海の生き物</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
+        <is>
+          <t>penguin</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>ペンギン</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>海の生き物</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
+        <is>
+          <t>crab</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>カニ</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t>海の生き物</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
+        <is>
+          <t>jellyfish</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>クラゲ</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t>海の生き物</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="inlineStr">
+        <is>
+          <t>sea turtle</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>ウミガメ</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>海の生き物</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>さかな</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>虫</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
+        <is>
+          <t>grasshopper</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>バッタ</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>虫</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
+        <is>
+          <t>ant</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>アリ</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>虫</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
+        <is>
+          <t>beetle</t>
+        </is>
+      </c>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>カブトムシ</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>虫</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
+        <is>
+          <t>stag beetle</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>クワガタ</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>虫</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>チョウ</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="5" t="inlineStr">
+        <is>
+          <t>虫</t>
+        </is>
+      </c>
+      <c r="B326" s="5" t="inlineStr">
+        <is>
+          <t>mantis</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t>カマキリ</t>
+        </is>
+      </c>
+      <c r="D326" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E326" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="5" t="inlineStr">
+        <is>
+          <t>虫</t>
+        </is>
+      </c>
+      <c r="B327" s="5" t="inlineStr">
+        <is>
+          <t>spider</t>
+        </is>
+      </c>
+      <c r="C327" s="5" t="inlineStr">
+        <is>
+          <t>クモ</t>
+        </is>
+      </c>
+      <c r="D327" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="5" t="inlineStr">
+        <is>
+          <t>虫</t>
+        </is>
+      </c>
+      <c r="B328" s="5" t="inlineStr">
+        <is>
+          <t>dragonfly</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>トンボ</t>
+        </is>
+      </c>
+      <c r="D328" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E328" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="5" t="inlineStr">
+        <is>
+          <t>性格</t>
+        </is>
+      </c>
+      <c r="B329" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t>活発な</t>
+        </is>
+      </c>
+      <c r="D329" s="5" t="inlineStr">
+        <is>
+          <t>He is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="5" t="inlineStr">
+        <is>
+          <t>性格</t>
+        </is>
+      </c>
+      <c r="B330" s="5" t="inlineStr">
+        <is>
+          <t>shy</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t>はずかしがりの</t>
+        </is>
+      </c>
+      <c r="D330" s="5" t="inlineStr">
+        <is>
+          <t>He is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="5" t="inlineStr">
+        <is>
+          <t>性格</t>
+        </is>
+      </c>
+      <c r="B331" s="5" t="inlineStr">
+        <is>
+          <t>smart</t>
+        </is>
+      </c>
+      <c r="C331" s="5" t="inlineStr">
+        <is>
+          <t>かしこい</t>
+        </is>
+      </c>
+      <c r="D331" s="5" t="inlineStr">
+        <is>
+          <t>He is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="5" t="inlineStr">
+        <is>
+          <t>性格</t>
+        </is>
+      </c>
+      <c r="B332" s="5" t="inlineStr">
+        <is>
+          <t>brave</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>ゆうかんな</t>
+        </is>
+      </c>
+      <c r="D332" s="5" t="inlineStr">
+        <is>
+          <t>He is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="5" t="inlineStr">
+        <is>
+          <t>性格</t>
+        </is>
+      </c>
+      <c r="B333" s="5" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="C333" s="5" t="inlineStr">
+        <is>
+          <t>つよい</t>
+        </is>
+      </c>
+      <c r="D333" s="5" t="inlineStr">
+        <is>
+          <t>He is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="5" t="inlineStr">
+        <is>
+          <t>性格</t>
+        </is>
+      </c>
+      <c r="B334" s="5" t="inlineStr">
+        <is>
+          <t>friendly</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>フレンドリーな</t>
+        </is>
+      </c>
+      <c r="D334" s="5" t="inlineStr">
+        <is>
+          <t>He is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="5" t="inlineStr">
+        <is>
+          <t>性格</t>
+        </is>
+      </c>
+      <c r="B335" s="5" t="inlineStr">
+        <is>
+          <t>funny</t>
+        </is>
+      </c>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t>おもしろい</t>
+        </is>
+      </c>
+      <c r="D335" s="5" t="inlineStr">
+        <is>
+          <t>He is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t>性格</t>
+        </is>
+      </c>
+      <c r="B336" s="5" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t>やさしい</t>
+        </is>
+      </c>
+      <c r="D336" s="5" t="inlineStr">
+        <is>
+          <t>He is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E336" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="B337" s="5" t="inlineStr">
+        <is>
+          <t>man</t>
+        </is>
+      </c>
+      <c r="C337" s="5" t="inlineStr">
+        <is>
+          <t>男の人</t>
+        </is>
+      </c>
+      <c r="D337" s="5" t="inlineStr">
+        <is>
+          <t>This is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="B338" s="5" t="inlineStr">
+        <is>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="inlineStr">
+        <is>
+          <t>女の人</t>
+        </is>
+      </c>
+      <c r="D338" s="5" t="inlineStr">
+        <is>
+          <t>This is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E338" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="B339" s="5" t="inlineStr">
+        <is>
+          <t>baby</t>
+        </is>
+      </c>
+      <c r="C339" s="5" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="D339" s="5" t="inlineStr">
+        <is>
+          <t>This is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E339" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="B340" s="5" t="inlineStr">
+        <is>
+          <t>boy</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="inlineStr">
+        <is>
+          <t>男の子</t>
+        </is>
+      </c>
+      <c r="D340" s="5" t="inlineStr">
+        <is>
+          <t>This is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="B341" s="5" t="inlineStr">
+        <is>
+          <t>girl</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t>女の子</t>
+        </is>
+      </c>
+      <c r="D341" s="5" t="inlineStr">
+        <is>
+          <t>This is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E341" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="B342" s="5" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
+          <t>子ども</t>
+        </is>
+      </c>
+      <c r="D342" s="5" t="inlineStr">
+        <is>
+          <t>This is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="B343" s="5" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t>友だち</t>
+        </is>
+      </c>
+      <c r="D343" s="5" t="inlineStr">
+        <is>
+          <t>This is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E343" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="B344" s="5" t="inlineStr">
+        <is>
+          <t>classmate</t>
+        </is>
+      </c>
+      <c r="C344" s="5" t="inlineStr">
+        <is>
+          <t>クラスメイト</t>
+        </is>
+      </c>
+      <c r="D344" s="5" t="inlineStr">
+        <is>
+          <t>This is ◯◯.</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B345" s="5" t="inlineStr">
+        <is>
+          <t>grandfather</t>
+        </is>
+      </c>
+      <c r="C345" s="5" t="inlineStr">
+        <is>
+          <t>おじいさん</t>
+        </is>
+      </c>
+      <c r="D345" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B346" s="5" t="inlineStr">
+        <is>
+          <t>grandmother</t>
+        </is>
+      </c>
+      <c r="C346" s="5" t="inlineStr">
+        <is>
+          <t>おばあさん</t>
+        </is>
+      </c>
+      <c r="D346" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B347" s="5" t="inlineStr">
+        <is>
+          <t>father</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t>お父さん</t>
+        </is>
+      </c>
+      <c r="D347" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B348" s="5" t="inlineStr">
+        <is>
+          <t>mother</t>
+        </is>
+      </c>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t>お母さん</t>
+        </is>
+      </c>
+      <c r="D348" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B349" s="5" t="inlineStr">
+        <is>
+          <t>parents</t>
+        </is>
+      </c>
+      <c r="C349" s="5" t="inlineStr">
+        <is>
+          <t>両親</t>
+        </is>
+      </c>
+      <c r="D349" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B350" s="5" t="inlineStr">
+        <is>
+          <t>grandparents</t>
+        </is>
+      </c>
+      <c r="C350" s="5" t="inlineStr">
+        <is>
+          <t>祖父母</t>
+        </is>
+      </c>
+      <c r="D350" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E350" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B351" s="5" t="inlineStr">
+        <is>
+          <t>brother</t>
+        </is>
+      </c>
+      <c r="C351" s="5" t="inlineStr">
+        <is>
+          <t>兄弟</t>
+        </is>
+      </c>
+      <c r="D351" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B352" s="5" t="inlineStr">
+        <is>
+          <t>sister</t>
+        </is>
+      </c>
+      <c r="C352" s="5" t="inlineStr">
+        <is>
+          <t>姉妹</t>
+        </is>
+      </c>
+      <c r="D352" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E352" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B353" s="5" t="inlineStr">
+        <is>
+          <t>cousin</t>
+        </is>
+      </c>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t>いとこ</t>
+        </is>
+      </c>
+      <c r="D353" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B354" s="5" t="inlineStr">
+        <is>
+          <t>uncle</t>
+        </is>
+      </c>
+      <c r="C354" s="5" t="inlineStr">
+        <is>
+          <t>おじ</t>
+        </is>
+      </c>
+      <c r="D354" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E354" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B355" s="5" t="inlineStr">
+        <is>
+          <t>aunt</t>
+        </is>
+      </c>
+      <c r="C355" s="5" t="inlineStr">
+        <is>
+          <t>おば</t>
+        </is>
+      </c>
+      <c r="D355" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E355" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B356" s="5" t="inlineStr">
+        <is>
+          <t>get up</t>
+        </is>
+      </c>
+      <c r="C356" s="5" t="inlineStr">
+        <is>
+          <t>起きる</t>
+        </is>
+      </c>
+      <c r="D356" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E356" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B357" s="5" t="inlineStr">
+        <is>
+          <t>comb my hair</t>
+        </is>
+      </c>
+      <c r="C357" s="5" t="inlineStr">
+        <is>
+          <t>髪をとかす</t>
+        </is>
+      </c>
+      <c r="D357" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B358" s="5" t="inlineStr">
+        <is>
+          <t>take out the garbage</t>
+        </is>
+      </c>
+      <c r="C358" s="5" t="inlineStr">
+        <is>
+          <t>ゴミを出す</t>
+        </is>
+      </c>
+      <c r="D358" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E358" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B359" s="5" t="inlineStr">
+        <is>
+          <t>get the newspaper</t>
+        </is>
+      </c>
+      <c r="C359" s="5" t="inlineStr">
+        <is>
+          <t>新聞を取る</t>
+        </is>
+      </c>
+      <c r="D359" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E359" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B360" s="5" t="inlineStr">
+        <is>
+          <t>have breakfast</t>
+        </is>
+      </c>
+      <c r="C360" s="5" t="inlineStr">
+        <is>
+          <t>朝食を食べる</t>
+        </is>
+      </c>
+      <c r="D360" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E360" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B361" s="5" t="inlineStr">
+        <is>
+          <t>brush my teeth</t>
+        </is>
+      </c>
+      <c r="C361" s="5" t="inlineStr">
+        <is>
+          <t>歯をみがく</t>
+        </is>
+      </c>
+      <c r="D361" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E361" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B362" s="5" t="inlineStr">
+        <is>
+          <t>go to school</t>
+        </is>
+      </c>
+      <c r="C362" s="5" t="inlineStr">
+        <is>
+          <t>学校へ行く</t>
+        </is>
+      </c>
+      <c r="D362" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E362" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B363" s="5" t="inlineStr">
+        <is>
+          <t>study English</t>
+        </is>
+      </c>
+      <c r="C363" s="5" t="inlineStr">
+        <is>
+          <t>英語を勉強する</t>
+        </is>
+      </c>
+      <c r="D363" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E363" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B364" s="5" t="inlineStr">
+        <is>
+          <t>have lunch</t>
+        </is>
+      </c>
+      <c r="C364" s="5" t="inlineStr">
+        <is>
+          <t>昼食を食べる</t>
+        </is>
+      </c>
+      <c r="D364" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E364" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B365" s="5" t="inlineStr">
+        <is>
+          <t>go home</t>
+        </is>
+      </c>
+      <c r="C365" s="5" t="inlineStr">
+        <is>
+          <t>家に帰る</t>
+        </is>
+      </c>
+      <c r="D365" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E365" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B366" s="5" t="inlineStr">
+        <is>
+          <t>do my homework</t>
+        </is>
+      </c>
+      <c r="C366" s="5" t="inlineStr">
+        <is>
+          <t>宿題をする</t>
+        </is>
+      </c>
+      <c r="D366" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E366" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B367" s="5" t="inlineStr">
+        <is>
+          <t>have dinner</t>
+        </is>
+      </c>
+      <c r="C367" s="5" t="inlineStr">
+        <is>
+          <t>夕食を食べる</t>
+        </is>
+      </c>
+      <c r="D367" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E367" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B368" s="5" t="inlineStr">
+        <is>
+          <t>wash the dishes</t>
+        </is>
+      </c>
+      <c r="C368" s="5" t="inlineStr">
+        <is>
+          <t>皿を洗う</t>
+        </is>
+      </c>
+      <c r="D368" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E368" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B369" s="5" t="inlineStr">
+        <is>
+          <t>watch TV</t>
+        </is>
+      </c>
+      <c r="C369" s="5" t="inlineStr">
+        <is>
+          <t>テレビを見る</t>
+        </is>
+      </c>
+      <c r="D369" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E369" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B370" s="5" t="inlineStr">
+        <is>
+          <t>take a bath</t>
+        </is>
+      </c>
+      <c r="C370" s="5" t="inlineStr">
+        <is>
+          <t>お風呂に入る</t>
+        </is>
+      </c>
+      <c r="D370" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E370" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B371" s="5" t="inlineStr">
+        <is>
+          <t>go to bed</t>
+        </is>
+      </c>
+      <c r="C371" s="5" t="inlineStr">
+        <is>
+          <t>寝る</t>
+        </is>
+      </c>
+      <c r="D371" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B372" s="5" t="inlineStr">
+        <is>
+          <t>shirt</t>
+        </is>
+      </c>
+      <c r="C372" s="5" t="inlineStr">
+        <is>
+          <t>シャツ</t>
+        </is>
+      </c>
+      <c r="D372" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E372" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B373" s="5" t="inlineStr">
+        <is>
+          <t>T-shirt</t>
+        </is>
+      </c>
+      <c r="C373" s="5" t="inlineStr">
+        <is>
+          <t>Tシャツ</t>
+        </is>
+      </c>
+      <c r="D373" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E373" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B374" s="5" t="inlineStr">
+        <is>
+          <t>sweatshirt</t>
+        </is>
+      </c>
+      <c r="C374" s="5" t="inlineStr">
+        <is>
+          <t>トレーナー</t>
+        </is>
+      </c>
+      <c r="D374" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E374" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B375" s="5" t="inlineStr">
+        <is>
+          <t>sweater</t>
+        </is>
+      </c>
+      <c r="C375" s="5" t="inlineStr">
+        <is>
+          <t>セーター</t>
+        </is>
+      </c>
+      <c r="D375" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E375" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B376" s="5" t="inlineStr">
+        <is>
+          <t>uniform</t>
+        </is>
+      </c>
+      <c r="C376" s="5" t="inlineStr">
+        <is>
+          <t>制服</t>
+        </is>
+      </c>
+      <c r="D376" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E376" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B377" s="5" t="inlineStr">
+        <is>
+          <t>pants</t>
+        </is>
+      </c>
+      <c r="C377" s="5" t="inlineStr">
+        <is>
+          <t>ズボン</t>
+        </is>
+      </c>
+      <c r="D377" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E377" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B378" s="5" t="inlineStr">
+        <is>
+          <t>jeans</t>
+        </is>
+      </c>
+      <c r="C378" s="5" t="inlineStr">
+        <is>
+          <t>ジーンズ</t>
+        </is>
+      </c>
+      <c r="D378" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E378" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B379" s="5" t="inlineStr">
+        <is>
+          <t>cap</t>
+        </is>
+      </c>
+      <c r="C379" s="5" t="inlineStr">
+        <is>
+          <t>ぼうし</t>
+        </is>
+      </c>
+      <c r="D379" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E379" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B380" s="5" t="inlineStr">
+        <is>
+          <t>hat</t>
+        </is>
+      </c>
+      <c r="C380" s="5" t="inlineStr">
+        <is>
+          <t>ぼうし</t>
+        </is>
+      </c>
+      <c r="D380" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E380" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B381" s="5" t="inlineStr">
+        <is>
+          <t>gloves</t>
+        </is>
+      </c>
+      <c r="C381" s="5" t="inlineStr">
+        <is>
+          <t>手ぶくろ</t>
+        </is>
+      </c>
+      <c r="D381" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E381" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B382" s="5" t="inlineStr">
+        <is>
+          <t>socks</t>
+        </is>
+      </c>
+      <c r="C382" s="5" t="inlineStr">
+        <is>
+          <t>くつ下</t>
+        </is>
+      </c>
+      <c r="D382" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E382" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B383" s="5" t="inlineStr">
+        <is>
+          <t>shoes</t>
+        </is>
+      </c>
+      <c r="C383" s="5" t="inlineStr">
+        <is>
+          <t>くつ</t>
+        </is>
+      </c>
+      <c r="D383" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E383" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B384" s="5" t="inlineStr">
+        <is>
+          <t>hair</t>
+        </is>
+      </c>
+      <c r="C384" s="5" t="inlineStr">
+        <is>
+          <t>かみの毛</t>
+        </is>
+      </c>
+      <c r="D384" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E384" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B385" s="5" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="C385" s="5" t="inlineStr">
+        <is>
+          <t>頭</t>
+        </is>
+      </c>
+      <c r="D385" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E385" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B386" s="5" t="inlineStr">
+        <is>
+          <t>face</t>
+        </is>
+      </c>
+      <c r="C386" s="5" t="inlineStr">
+        <is>
+          <t>顔</t>
+        </is>
+      </c>
+      <c r="D386" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E386" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B387" s="5" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="C387" s="5" t="inlineStr">
+        <is>
+          <t>かた</t>
+        </is>
+      </c>
+      <c r="D387" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E387" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B388" s="5" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="C388" s="5" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="D388" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E388" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B389" s="5" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="C389" s="5" t="inlineStr">
+        <is>
+          <t>うで</t>
+        </is>
+      </c>
+      <c r="D389" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E389" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B390" s="5" t="inlineStr">
+        <is>
+          <t>knee</t>
+        </is>
+      </c>
+      <c r="C390" s="5" t="inlineStr">
+        <is>
+          <t>ひざ</t>
+        </is>
+      </c>
+      <c r="D390" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E390" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B391" s="5" t="inlineStr">
+        <is>
+          <t>eye</t>
+        </is>
+      </c>
+      <c r="C391" s="5" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="D391" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E391" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B392" s="5" t="inlineStr">
+        <is>
+          <t>ear</t>
+        </is>
+      </c>
+      <c r="C392" s="5" t="inlineStr">
+        <is>
+          <t>耳</t>
+        </is>
+      </c>
+      <c r="D392" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E392" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B393" s="5" t="inlineStr">
+        <is>
+          <t>nose</t>
+        </is>
+      </c>
+      <c r="C393" s="5" t="inlineStr">
+        <is>
+          <t>鼻</t>
+        </is>
+      </c>
+      <c r="D393" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E393" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B394" s="5" t="inlineStr">
+        <is>
+          <t>mouth</t>
+        </is>
+      </c>
+      <c r="C394" s="5" t="inlineStr">
+        <is>
+          <t>口</t>
+        </is>
+      </c>
+      <c r="D394" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E394" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B395" s="5" t="inlineStr">
+        <is>
+          <t>teeth</t>
+        </is>
+      </c>
+      <c r="C395" s="5" t="inlineStr">
+        <is>
+          <t>歯</t>
+        </is>
+      </c>
+      <c r="D395" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E395" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B396" s="5" t="inlineStr">
+        <is>
+          <t>neck</t>
+        </is>
+      </c>
+      <c r="C396" s="5" t="inlineStr">
+        <is>
+          <t>首</t>
+        </is>
+      </c>
+      <c r="D396" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E396" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B397" s="5" t="inlineStr">
+        <is>
+          <t>leg</t>
+        </is>
+      </c>
+      <c r="C397" s="5" t="inlineStr">
+        <is>
+          <t>足</t>
+        </is>
+      </c>
+      <c r="D397" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E397" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B398" s="5" t="inlineStr">
+        <is>
+          <t>toe</t>
+        </is>
+      </c>
+      <c r="C398" s="5" t="inlineStr">
+        <is>
+          <t>つま先</t>
+        </is>
+      </c>
+      <c r="D398" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="E398" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B399" s="5" t="inlineStr">
+        <is>
+          <t>classroom</t>
+        </is>
+      </c>
+      <c r="C399" s="5" t="inlineStr">
+        <is>
+          <t>教室</t>
+        </is>
+      </c>
+      <c r="D399" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E399" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B400" s="5" t="inlineStr">
+        <is>
+          <t>computer room</t>
+        </is>
+      </c>
+      <c r="C400" s="5" t="inlineStr">
+        <is>
+          <t>コンピュータ室</t>
+        </is>
+      </c>
+      <c r="D400" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E400" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B401" s="5" t="inlineStr">
+        <is>
+          <t>entrance</t>
+        </is>
+      </c>
+      <c r="C401" s="5" t="inlineStr">
+        <is>
+          <t>げんかん</t>
+        </is>
+      </c>
+      <c r="D401" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E401" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B402" s="5" t="inlineStr">
+        <is>
+          <t>gym</t>
+        </is>
+      </c>
+      <c r="C402" s="5" t="inlineStr">
+        <is>
+          <t>体育館</t>
+        </is>
+      </c>
+      <c r="D402" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E402" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B403" s="5" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="C403" s="5" t="inlineStr">
+        <is>
+          <t>図書室</t>
+        </is>
+      </c>
+      <c r="D403" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E403" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B404" s="5" t="inlineStr">
+        <is>
+          <t>music room</t>
+        </is>
+      </c>
+      <c r="C404" s="5" t="inlineStr">
+        <is>
+          <t>音楽室</t>
+        </is>
+      </c>
+      <c r="D404" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E404" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B405" s="5" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="C405" s="5" t="inlineStr">
+        <is>
+          <t>校庭</t>
+        </is>
+      </c>
+      <c r="D405" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E405" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B406" s="5" t="inlineStr">
+        <is>
+          <t>school nurse's office</t>
+        </is>
+      </c>
+      <c r="C406" s="5" t="inlineStr">
+        <is>
+          <t>保健室</t>
+        </is>
+      </c>
+      <c r="D406" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E406" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B407" s="5" t="inlineStr">
+        <is>
+          <t>restroom</t>
+        </is>
+      </c>
+      <c r="C407" s="5" t="inlineStr">
+        <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="D407" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E407" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B408" s="5" t="inlineStr">
+        <is>
+          <t>swimming pool</t>
+        </is>
+      </c>
+      <c r="C408" s="5" t="inlineStr">
+        <is>
+          <t>プール</t>
+        </is>
+      </c>
+      <c r="D408" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E408" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B409" s="5" t="inlineStr">
+        <is>
+          <t>teachers' office</t>
+        </is>
+      </c>
+      <c r="C409" s="5" t="inlineStr">
+        <is>
+          <t>職員室</t>
+        </is>
+      </c>
+      <c r="D409" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E409" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B410" s="5" t="inlineStr">
+        <is>
+          <t>school principal's office</t>
+        </is>
+      </c>
+      <c r="C410" s="5" t="inlineStr">
+        <is>
+          <t>校長室</t>
+        </is>
+      </c>
+      <c r="D410" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E410" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B411" s="5" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
+      <c r="C411" s="5" t="inlineStr">
+        <is>
+          <t>クレヨン</t>
+        </is>
+      </c>
+      <c r="D411" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E411" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B412" s="5" t="inlineStr">
+        <is>
+          <t>marker</t>
+        </is>
+      </c>
+      <c r="C412" s="5" t="inlineStr">
+        <is>
+          <t>マーカー</t>
+        </is>
+      </c>
+      <c r="D412" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E412" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B413" s="5" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="C413" s="5" t="inlineStr">
+        <is>
+          <t>ペン</t>
+        </is>
+      </c>
+      <c r="D413" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E413" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B414" s="5" t="inlineStr">
+        <is>
+          <t>pencil</t>
+        </is>
+      </c>
+      <c r="C414" s="5" t="inlineStr">
+        <is>
+          <t>えんぴつ</t>
+        </is>
+      </c>
+      <c r="D414" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E414" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B415" s="5" t="inlineStr">
+        <is>
+          <t>pencil case</t>
+        </is>
+      </c>
+      <c r="C415" s="5" t="inlineStr">
+        <is>
+          <t>筆箱</t>
+        </is>
+      </c>
+      <c r="D415" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E415" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B416" s="5" t="inlineStr">
+        <is>
+          <t>eraser</t>
+        </is>
+      </c>
+      <c r="C416" s="5" t="inlineStr">
+        <is>
+          <t>消しゴム</t>
+        </is>
+      </c>
+      <c r="D416" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E416" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B417" s="5" t="inlineStr">
+        <is>
+          <t>ruler</t>
+        </is>
+      </c>
+      <c r="C417" s="5" t="inlineStr">
+        <is>
+          <t>じょうぎ</t>
+        </is>
+      </c>
+      <c r="D417" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E417" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B418" s="5" t="inlineStr">
+        <is>
+          <t>glue</t>
+        </is>
+      </c>
+      <c r="C418" s="5" t="inlineStr">
+        <is>
+          <t>のり</t>
+        </is>
+      </c>
+      <c r="D418" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E418" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B419" s="5" t="inlineStr">
+        <is>
+          <t>scissors</t>
+        </is>
+      </c>
+      <c r="C419" s="5" t="inlineStr">
+        <is>
+          <t>はさみ</t>
+        </is>
+      </c>
+      <c r="D419" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E419" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B420" s="5" t="inlineStr">
+        <is>
+          <t>stapler</t>
+        </is>
+      </c>
+      <c r="C420" s="5" t="inlineStr">
+        <is>
+          <t>ホチキス</t>
+        </is>
+      </c>
+      <c r="D420" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E420" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B421" s="5" t="inlineStr">
+        <is>
+          <t>notebook</t>
+        </is>
+      </c>
+      <c r="C421" s="5" t="inlineStr">
+        <is>
+          <t>ノート</t>
+        </is>
+      </c>
+      <c r="D421" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E421" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B422" s="5" t="inlineStr">
+        <is>
+          <t>pencil sharpener</t>
+        </is>
+      </c>
+      <c r="C422" s="5" t="inlineStr">
+        <is>
+          <t>えんぴつけずり</t>
+        </is>
+      </c>
+      <c r="D422" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E422" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="5" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+      <c r="B423" s="5" t="inlineStr">
+        <is>
+          <t>recorder</t>
+        </is>
+      </c>
+      <c r="C423" s="5" t="inlineStr">
+        <is>
+          <t>リコーダー</t>
+        </is>
+      </c>
+      <c r="D423" s="5" t="inlineStr">
+        <is>
+          <t>I can play the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E423" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="5" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+      <c r="B424" s="5" t="inlineStr">
+        <is>
+          <t>harmonica</t>
+        </is>
+      </c>
+      <c r="C424" s="5" t="inlineStr">
+        <is>
+          <t>ハーモニカ</t>
+        </is>
+      </c>
+      <c r="D424" s="5" t="inlineStr">
+        <is>
+          <t>I can play the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E424" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="5" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+      <c r="B425" s="5" t="inlineStr">
+        <is>
+          <t>triangle</t>
+        </is>
+      </c>
+      <c r="C425" s="5" t="inlineStr">
+        <is>
+          <t>トライアングル</t>
+        </is>
+      </c>
+      <c r="D425" s="5" t="inlineStr">
+        <is>
+          <t>I can play the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E425" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="5" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+      <c r="B426" s="5" t="inlineStr">
+        <is>
+          <t>piano</t>
+        </is>
+      </c>
+      <c r="C426" s="5" t="inlineStr">
+        <is>
+          <t>ピアノ</t>
+        </is>
+      </c>
+      <c r="D426" s="5" t="inlineStr">
+        <is>
+          <t>I can play the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E426" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="5" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+      <c r="B427" s="5" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="C427" s="5" t="inlineStr">
+        <is>
+          <t>ギター</t>
+        </is>
+      </c>
+      <c r="D427" s="5" t="inlineStr">
+        <is>
+          <t>I can play the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E427" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="5" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+      <c r="B428" s="5" t="inlineStr">
+        <is>
+          <t>violin</t>
+        </is>
+      </c>
+      <c r="C428" s="5" t="inlineStr">
+        <is>
+          <t>バイオリン</t>
+        </is>
+      </c>
+      <c r="D428" s="5" t="inlineStr">
+        <is>
+          <t>I can play the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E428" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="5" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+      <c r="B429" s="5" t="inlineStr">
+        <is>
+          <t>drum</t>
+        </is>
+      </c>
+      <c r="C429" s="5" t="inlineStr">
+        <is>
+          <t>ドラム</t>
+        </is>
+      </c>
+      <c r="D429" s="5" t="inlineStr">
+        <is>
+          <t>I can play the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E429" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="5" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+      <c r="B430" s="5" t="inlineStr">
+        <is>
+          <t>xylophone</t>
+        </is>
+      </c>
+      <c r="C430" s="5" t="inlineStr">
+        <is>
+          <t>もっきん</t>
+        </is>
+      </c>
+      <c r="D430" s="5" t="inlineStr">
+        <is>
+          <t>I can play the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E430" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="5" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+      <c r="B431" s="5" t="inlineStr">
+        <is>
+          <t>keyboard harmonica</t>
+        </is>
+      </c>
+      <c r="C431" s="5" t="inlineStr">
+        <is>
+          <t>けんばんハーモニカ</t>
+        </is>
+      </c>
+      <c r="D431" s="5" t="inlineStr">
+        <is>
+          <t>I can play the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E431" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B432" s="5" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="C432" s="5" t="inlineStr">
+        <is>
+          <t>かばん</t>
+        </is>
+      </c>
+      <c r="D432" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E432" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B433" s="5" t="inlineStr">
+        <is>
+          <t>bat</t>
+        </is>
+      </c>
+      <c r="C433" s="5" t="inlineStr">
+        <is>
+          <t>バット</t>
+        </is>
+      </c>
+      <c r="D433" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E433" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B434" s="5" t="inlineStr">
+        <is>
+          <t>glove</t>
+        </is>
+      </c>
+      <c r="C434" s="5" t="inlineStr">
+        <is>
+          <t>グローブ</t>
+        </is>
+      </c>
+      <c r="D434" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E434" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B435" s="5" t="inlineStr">
+        <is>
+          <t>racket</t>
+        </is>
+      </c>
+      <c r="C435" s="5" t="inlineStr">
+        <is>
+          <t>ラケット</t>
+        </is>
+      </c>
+      <c r="D435" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E435" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B436" s="5" t="inlineStr">
+        <is>
+          <t>soccer shoes</t>
+        </is>
+      </c>
+      <c r="C436" s="5" t="inlineStr">
+        <is>
+          <t>サッカーシューズ</t>
+        </is>
+      </c>
+      <c r="D436" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E436" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B437" s="5" t="inlineStr">
+        <is>
+          <t>umbrella</t>
+        </is>
+      </c>
+      <c r="C437" s="5" t="inlineStr">
+        <is>
+          <t>かさ</t>
+        </is>
+      </c>
+      <c r="D437" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E437" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B438" s="5" t="inlineStr">
+        <is>
+          <t>glass</t>
+        </is>
+      </c>
+      <c r="C438" s="5" t="inlineStr">
+        <is>
+          <t>コップ</t>
+        </is>
+      </c>
+      <c r="D438" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E438" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B439" s="5" t="inlineStr">
+        <is>
+          <t>mug</t>
+        </is>
+      </c>
+      <c r="C439" s="5" t="inlineStr">
+        <is>
+          <t>マグカップ</t>
+        </is>
+      </c>
+      <c r="D439" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E439" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B440" s="5" t="inlineStr">
+        <is>
+          <t>textbook</t>
+        </is>
+      </c>
+      <c r="C440" s="5" t="inlineStr">
+        <is>
+          <t>教科書</t>
+        </is>
+      </c>
+      <c r="D440" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E440" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B441" s="5" t="inlineStr">
+        <is>
+          <t>comic book</t>
+        </is>
+      </c>
+      <c r="C441" s="5" t="inlineStr">
+        <is>
+          <t>まんが</t>
+        </is>
+      </c>
+      <c r="D441" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E441" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B442" s="5" t="inlineStr">
+        <is>
+          <t>dictionary</t>
+        </is>
+      </c>
+      <c r="C442" s="5" t="inlineStr">
+        <is>
+          <t>辞書</t>
+        </is>
+      </c>
+      <c r="D442" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E442" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B443" s="5" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="C443" s="5" t="inlineStr">
+        <is>
+          <t>プレゼント</t>
+        </is>
+      </c>
+      <c r="D443" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E443" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B444" s="5" t="inlineStr">
+        <is>
+          <t>treasure</t>
+        </is>
+      </c>
+      <c r="C444" s="5" t="inlineStr">
+        <is>
+          <t>たから物</t>
+        </is>
+      </c>
+      <c r="D444" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E444" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B445" s="5" t="inlineStr">
+        <is>
+          <t>sticker</t>
+        </is>
+      </c>
+      <c r="C445" s="5" t="inlineStr">
+        <is>
+          <t>シール</t>
+        </is>
+      </c>
+      <c r="D445" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E445" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B446" s="5" t="inlineStr">
+        <is>
+          <t>ticket</t>
+        </is>
+      </c>
+      <c r="C446" s="5" t="inlineStr">
+        <is>
+          <t>チケット</t>
+        </is>
+      </c>
+      <c r="D446" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E446" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B447" s="5" t="inlineStr">
+        <is>
+          <t>watch</t>
+        </is>
+      </c>
+      <c r="C447" s="5" t="inlineStr">
+        <is>
+          <t>うで時計</t>
+        </is>
+      </c>
+      <c r="D447" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E447" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B448" s="5" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C448" s="5" t="inlineStr">
+        <is>
+          <t>テレビ</t>
+        </is>
+      </c>
+      <c r="D448" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E448" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B449" s="5" t="inlineStr">
+        <is>
+          <t>computer</t>
+        </is>
+      </c>
+      <c r="C449" s="5" t="inlineStr">
+        <is>
+          <t>コンピュータ</t>
+        </is>
+      </c>
+      <c r="D449" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E449" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B450" s="5" t="inlineStr">
+        <is>
+          <t>smartphone</t>
+        </is>
+      </c>
+      <c r="C450" s="5" t="inlineStr">
+        <is>
+          <t>スマートフォン</t>
+        </is>
+      </c>
+      <c r="D450" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E450" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B451" s="5" t="inlineStr">
+        <is>
+          <t>tablet</t>
+        </is>
+      </c>
+      <c r="C451" s="5" t="inlineStr">
+        <is>
+          <t>タブレット</t>
+        </is>
+      </c>
+      <c r="D451" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E451" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B452" s="5" t="inlineStr">
+        <is>
+          <t>desk</t>
+        </is>
+      </c>
+      <c r="C452" s="5" t="inlineStr">
+        <is>
+          <t>つくえ</t>
+        </is>
+      </c>
+      <c r="D452" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E452" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B453" s="5" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="C453" s="5" t="inlineStr">
+        <is>
+          <t>いす</t>
+        </is>
+      </c>
+      <c r="D453" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E453" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B454" s="5" t="inlineStr">
+        <is>
+          <t>bed</t>
+        </is>
+      </c>
+      <c r="C454" s="5" t="inlineStr">
+        <is>
+          <t>ベッド</t>
+        </is>
+      </c>
+      <c r="D454" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="E454" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B455" s="5" t="inlineStr">
+        <is>
+          <t>camping</t>
+        </is>
+      </c>
+      <c r="C455" s="5" t="inlineStr">
+        <is>
+          <t>キャンプ</t>
+        </is>
+      </c>
+      <c r="D455" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E455" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B456" s="5" t="inlineStr">
+        <is>
+          <t>dancing</t>
+        </is>
+      </c>
+      <c r="C456" s="5" t="inlineStr">
+        <is>
+          <t>ダンス</t>
+        </is>
+      </c>
+      <c r="D456" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E456" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B457" s="5" t="inlineStr">
+        <is>
+          <t>fishing</t>
+        </is>
+      </c>
+      <c r="C457" s="5" t="inlineStr">
+        <is>
+          <t>つり</t>
+        </is>
+      </c>
+      <c r="D457" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E457" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B458" s="5" t="inlineStr">
+        <is>
+          <t>hiking</t>
+        </is>
+      </c>
+      <c r="C458" s="5" t="inlineStr">
+        <is>
+          <t>ハイキング</t>
+        </is>
+      </c>
+      <c r="D458" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E458" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B459" s="5" t="inlineStr">
+        <is>
+          <t>shopping</t>
+        </is>
+      </c>
+      <c r="C459" s="5" t="inlineStr">
+        <is>
+          <t>買い物</t>
+        </is>
+      </c>
+      <c r="D459" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E459" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B460" s="5" t="inlineStr">
+        <is>
+          <t>reading</t>
+        </is>
+      </c>
+      <c r="C460" s="5" t="inlineStr">
+        <is>
+          <t>読書</t>
+        </is>
+      </c>
+      <c r="D460" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E460" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B461" s="5" t="inlineStr">
+        <is>
+          <t>drawing</t>
+        </is>
+      </c>
+      <c r="C461" s="5" t="inlineStr">
+        <is>
+          <t>絵をかくこと</t>
+        </is>
+      </c>
+      <c r="D461" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E461" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B462" s="5" t="inlineStr">
+        <is>
+          <t>jogging</t>
+        </is>
+      </c>
+      <c r="C462" s="5" t="inlineStr">
+        <is>
+          <t>ジョギング</t>
+        </is>
+      </c>
+      <c r="D462" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E462" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B463" s="5" t="inlineStr">
+        <is>
+          <t>swinging</t>
+        </is>
+      </c>
+      <c r="C463" s="5" t="inlineStr">
+        <is>
+          <t>ブランコ</t>
+        </is>
+      </c>
+      <c r="D463" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E463" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B464" s="5" t="inlineStr">
+        <is>
+          <t>playing the piano</t>
+        </is>
+      </c>
+      <c r="C464" s="5" t="inlineStr">
+        <is>
+          <t>ピアノをひくこと</t>
+        </is>
+      </c>
+      <c r="D464" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E464" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B465" s="5" t="inlineStr">
+        <is>
+          <t>playing video games</t>
+        </is>
+      </c>
+      <c r="C465" s="5" t="inlineStr">
+        <is>
+          <t>ゲームをすること</t>
+        </is>
+      </c>
+      <c r="D465" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E465" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B466" s="5" t="inlineStr">
+        <is>
+          <t>seeing movies</t>
+        </is>
+      </c>
+      <c r="C466" s="5" t="inlineStr">
+        <is>
+          <t>映画を見ること</t>
+        </is>
+      </c>
+      <c r="D466" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E466" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B467" s="5" t="inlineStr">
+        <is>
+          <t>cards</t>
+        </is>
+      </c>
+      <c r="C467" s="5" t="inlineStr">
+        <is>
+          <t>トランプ</t>
+        </is>
+      </c>
+      <c r="D467" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E467" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B468" s="5" t="inlineStr">
+        <is>
+          <t>jump rope</t>
+        </is>
+      </c>
+      <c r="C468" s="5" t="inlineStr">
+        <is>
+          <t>なわとび</t>
+        </is>
+      </c>
+      <c r="D468" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E468" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B469" s="5" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="C469" s="5" t="inlineStr">
+        <is>
+          <t>おにごっこ</t>
+        </is>
+      </c>
+      <c r="D469" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E469" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B470" s="5" t="inlineStr">
+        <is>
+          <t>hide-and-seek</t>
+        </is>
+      </c>
+      <c r="C470" s="5" t="inlineStr">
+        <is>
+          <t>かくれんぼ</t>
+        </is>
+      </c>
+      <c r="D470" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E470" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B471" s="5" t="inlineStr">
+        <is>
+          <t>rock-paper-scissors</t>
+        </is>
+      </c>
+      <c r="C471" s="5" t="inlineStr">
+        <is>
+          <t>じゃんけん</t>
+        </is>
+      </c>
+      <c r="D471" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E471" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B472" s="5" t="inlineStr">
+        <is>
+          <t>field trip</t>
+        </is>
+      </c>
+      <c r="C472" s="5" t="inlineStr">
+        <is>
+          <t>遠足</t>
+        </is>
+      </c>
+      <c r="D472" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E472" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B473" s="5" t="inlineStr">
+        <is>
+          <t>school trip</t>
+        </is>
+      </c>
+      <c r="C473" s="5" t="inlineStr">
+        <is>
+          <t>修学旅行</t>
+        </is>
+      </c>
+      <c r="D473" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E473" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B474" s="5" t="inlineStr">
+        <is>
+          <t>chorus contest</t>
+        </is>
+      </c>
+      <c r="C474" s="5" t="inlineStr">
+        <is>
+          <t>合唱コンクール</t>
+        </is>
+      </c>
+      <c r="D474" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E474" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B475" s="5" t="inlineStr">
+        <is>
+          <t>volunteer day</t>
+        </is>
+      </c>
+      <c r="C475" s="5" t="inlineStr">
+        <is>
+          <t>ボランティアの日</t>
+        </is>
+      </c>
+      <c r="D475" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E475" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B476" s="5" t="inlineStr">
+        <is>
+          <t>drama festival</t>
+        </is>
+      </c>
+      <c r="C476" s="5" t="inlineStr">
+        <is>
+          <t>劇の発表会</t>
+        </is>
+      </c>
+      <c r="D476" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E476" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B477" s="5" t="inlineStr">
+        <is>
+          <t>music festival</t>
+        </is>
+      </c>
+      <c r="C477" s="5" t="inlineStr">
+        <is>
+          <t>音楽会</t>
+        </is>
+      </c>
+      <c r="D477" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E477" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B478" s="5" t="inlineStr">
+        <is>
+          <t>school festival</t>
+        </is>
+      </c>
+      <c r="C478" s="5" t="inlineStr">
+        <is>
+          <t>学園祭</t>
+        </is>
+      </c>
+      <c r="D478" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E478" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B479" s="5" t="inlineStr">
+        <is>
+          <t>sports day</t>
+        </is>
+      </c>
+      <c r="C479" s="5" t="inlineStr">
+        <is>
+          <t>運動会</t>
+        </is>
+      </c>
+      <c r="D479" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E479" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B480" s="5" t="inlineStr">
+        <is>
+          <t>evacuation drill</t>
+        </is>
+      </c>
+      <c r="C480" s="5" t="inlineStr">
+        <is>
+          <t>ひなん訓練</t>
+        </is>
+      </c>
+      <c r="D480" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E480" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B481" s="5" t="inlineStr">
+        <is>
+          <t>swimming meet</t>
+        </is>
+      </c>
+      <c r="C481" s="5" t="inlineStr">
+        <is>
+          <t>水泳大会</t>
+        </is>
+      </c>
+      <c r="D481" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E481" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B482" s="5" t="inlineStr">
+        <is>
+          <t>summer vacation</t>
+        </is>
+      </c>
+      <c r="C482" s="5" t="inlineStr">
+        <is>
+          <t>夏休み</t>
+        </is>
+      </c>
+      <c r="D482" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E482" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B483" s="5" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C483" s="5" t="inlineStr">
+        <is>
+          <t>思い出</t>
+        </is>
+      </c>
+      <c r="D483" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E483" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B484" s="5" t="inlineStr">
+        <is>
+          <t>entrance ceremony</t>
+        </is>
+      </c>
+      <c r="C484" s="5" t="inlineStr">
+        <is>
+          <t>入学式</t>
+        </is>
+      </c>
+      <c r="D484" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E484" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B485" s="5" t="inlineStr">
+        <is>
+          <t>graduation ceremony</t>
+        </is>
+      </c>
+      <c r="C485" s="5" t="inlineStr">
+        <is>
+          <t>卒業式</t>
+        </is>
+      </c>
+      <c r="D485" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E485" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B486" s="5" t="inlineStr">
+        <is>
+          <t>birthday</t>
+        </is>
+      </c>
+      <c r="C486" s="5" t="inlineStr">
+        <is>
+          <t>誕生日</t>
+        </is>
+      </c>
+      <c r="D486" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E486" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B487" s="5" t="inlineStr">
+        <is>
+          <t>New Year's Day</t>
+        </is>
+      </c>
+      <c r="C487" s="5" t="inlineStr">
+        <is>
+          <t>元日</t>
+        </is>
+      </c>
+      <c r="D487" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E487" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B488" s="5" t="inlineStr">
+        <is>
+          <t>Dolls' Festival</t>
+        </is>
+      </c>
+      <c r="C488" s="5" t="inlineStr">
+        <is>
+          <t>ひな祭り</t>
+        </is>
+      </c>
+      <c r="D488" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E488" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B489" s="5" t="inlineStr">
+        <is>
+          <t>cherry blossom viewing</t>
+        </is>
+      </c>
+      <c r="C489" s="5" t="inlineStr">
+        <is>
+          <t>お花見</t>
+        </is>
+      </c>
+      <c r="D489" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E489" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B490" s="5" t="inlineStr">
+        <is>
+          <t>Children's Day</t>
+        </is>
+      </c>
+      <c r="C490" s="5" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
+      <c r="D490" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E490" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B491" s="5" t="inlineStr">
+        <is>
+          <t>Star Festival</t>
+        </is>
+      </c>
+      <c r="C491" s="5" t="inlineStr">
+        <is>
+          <t>七夕</t>
+        </is>
+      </c>
+      <c r="D491" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E491" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B492" s="5" t="inlineStr">
+        <is>
+          <t>fireworks festival</t>
+        </is>
+      </c>
+      <c r="C492" s="5" t="inlineStr">
+        <is>
+          <t>花火大会</t>
+        </is>
+      </c>
+      <c r="D492" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E492" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B493" s="5" t="inlineStr">
+        <is>
+          <t>Halloween</t>
+        </is>
+      </c>
+      <c r="C493" s="5" t="inlineStr">
+        <is>
+          <t>ハロウィン</t>
+        </is>
+      </c>
+      <c r="D493" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E493" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B494" s="5" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="C494" s="5" t="inlineStr">
+        <is>
+          <t>クリスマス</t>
+        </is>
+      </c>
+      <c r="D494" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E494" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B495" s="5" t="inlineStr">
+        <is>
+          <t>New Year's Eve</t>
+        </is>
+      </c>
+      <c r="C495" s="5" t="inlineStr">
+        <is>
+          <t>大みそか</t>
+        </is>
+      </c>
+      <c r="D495" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="E495" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B496" s="5" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C496" s="5" t="inlineStr">
+        <is>
+          <t>よい</t>
+        </is>
+      </c>
+      <c r="D496" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E496" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B497" s="5" t="inlineStr">
+        <is>
+          <t>great</t>
+        </is>
+      </c>
+      <c r="C497" s="5" t="inlineStr">
+        <is>
+          <t>すばらしい</t>
+        </is>
+      </c>
+      <c r="D497" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E497" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B498" s="5" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C498" s="5" t="inlineStr">
+        <is>
+          <t>わるい</t>
+        </is>
+      </c>
+      <c r="D498" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E498" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B499" s="5" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="C499" s="5" t="inlineStr">
+        <is>
+          <t>すてきな</t>
+        </is>
+      </c>
+      <c r="D499" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E499" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B500" s="5" t="inlineStr">
+        <is>
+          <t>amazing</t>
+        </is>
+      </c>
+      <c r="C500" s="5" t="inlineStr">
+        <is>
+          <t>おどろくべき</t>
+        </is>
+      </c>
+      <c r="D500" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E500" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B501" s="5" t="inlineStr">
+        <is>
+          <t>fantastic</t>
+        </is>
+      </c>
+      <c r="C501" s="5" t="inlineStr">
+        <is>
+          <t>すごくよい</t>
+        </is>
+      </c>
+      <c r="D501" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E501" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B502" s="5" t="inlineStr">
+        <is>
+          <t>wonderful</t>
+        </is>
+      </c>
+      <c r="C502" s="5" t="inlineStr">
+        <is>
+          <t>すばらしい</t>
+        </is>
+      </c>
+      <c r="D502" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E502" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B503" s="5" t="inlineStr">
+        <is>
+          <t>beautiful</t>
+        </is>
+      </c>
+      <c r="C503" s="5" t="inlineStr">
+        <is>
+          <t>美しい</t>
+        </is>
+      </c>
+      <c r="D503" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E503" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B504" s="5" t="inlineStr">
+        <is>
+          <t>cool</t>
+        </is>
+      </c>
+      <c r="C504" s="5" t="inlineStr">
+        <is>
+          <t>かっこいい</t>
+        </is>
+      </c>
+      <c r="D504" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E504" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B505" s="5" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="C505" s="5" t="inlineStr">
+        <is>
+          <t>かわいい</t>
+        </is>
+      </c>
+      <c r="D505" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E505" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B506" s="5" t="inlineStr">
+        <is>
+          <t>favorite</t>
+        </is>
+      </c>
+      <c r="C506" s="5" t="inlineStr">
+        <is>
+          <t>お気に入りの</t>
+        </is>
+      </c>
+      <c r="D506" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E506" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B507" s="5" t="inlineStr">
+        <is>
+          <t>interesting</t>
+        </is>
+      </c>
+      <c r="C507" s="5" t="inlineStr">
+        <is>
+          <t>おもしろい</t>
+        </is>
+      </c>
+      <c r="D507" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E507" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B508" s="5" t="inlineStr">
+        <is>
+          <t>exciting</t>
+        </is>
+      </c>
+      <c r="C508" s="5" t="inlineStr">
+        <is>
+          <t>わくわくする</t>
+        </is>
+      </c>
+      <c r="D508" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E508" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B509" s="5" t="inlineStr">
+        <is>
+          <t>famous</t>
+        </is>
+      </c>
+      <c r="C509" s="5" t="inlineStr">
+        <is>
+          <t>有名な</t>
+        </is>
+      </c>
+      <c r="D509" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E509" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B510" s="5" t="inlineStr">
+        <is>
+          <t>popular</t>
+        </is>
+      </c>
+      <c r="C510" s="5" t="inlineStr">
+        <is>
+          <t>人気の</t>
+        </is>
+      </c>
+      <c r="D510" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E510" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B511" s="5" t="inlineStr">
+        <is>
+          <t>colorful</t>
+        </is>
+      </c>
+      <c r="C511" s="5" t="inlineStr">
+        <is>
+          <t>カラフルな</t>
+        </is>
+      </c>
+      <c r="D511" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E511" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B512" s="5" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="C512" s="5" t="inlineStr">
+        <is>
+          <t>国際的な</t>
+        </is>
+      </c>
+      <c r="D512" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E512" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B513" s="5" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="C513" s="5" t="inlineStr">
+        <is>
+          <t>楽しい</t>
+        </is>
+      </c>
+      <c r="D513" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E513" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B514" s="5" t="inlineStr">
+        <is>
+          <t>big</t>
+        </is>
+      </c>
+      <c r="C514" s="5" t="inlineStr">
+        <is>
+          <t>大きい</t>
+        </is>
+      </c>
+      <c r="D514" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E514" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B515" s="5" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="C515" s="5" t="inlineStr">
+        <is>
+          <t>小さい</t>
+        </is>
+      </c>
+      <c r="D515" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E515" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B516" s="5" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="C516" s="5" t="inlineStr">
+        <is>
+          <t>長い</t>
+        </is>
+      </c>
+      <c r="D516" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E516" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B517" s="5" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C517" s="5" t="inlineStr">
+        <is>
+          <t>短い</t>
+        </is>
+      </c>
+      <c r="D517" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E517" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B518" s="5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="C518" s="5" t="inlineStr">
+        <is>
+          <t>新しい</t>
+        </is>
+      </c>
+      <c r="D518" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E518" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B519" s="5" t="inlineStr">
+        <is>
+          <t>old</t>
+        </is>
+      </c>
+      <c r="C519" s="5" t="inlineStr">
+        <is>
+          <t>古い</t>
+        </is>
+      </c>
+      <c r="D519" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E519" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B520" s="5" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="C520" s="5" t="inlineStr">
+        <is>
+          <t>速い</t>
+        </is>
+      </c>
+      <c r="D520" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E520" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B521" s="5" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="C521" s="5" t="inlineStr">
+        <is>
+          <t>おそい</t>
+        </is>
+      </c>
+      <c r="D521" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E521" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B522" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C522" s="5" t="inlineStr">
+        <is>
+          <t>高い</t>
+        </is>
+      </c>
+      <c r="D522" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E522" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B523" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C523" s="5" t="inlineStr">
+        <is>
+          <t>低い</t>
+        </is>
+      </c>
+      <c r="D523" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="E523" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B524" s="5" t="inlineStr">
+        <is>
+          <t>artist</t>
+        </is>
+      </c>
+      <c r="C524" s="5" t="inlineStr">
+        <is>
+          <t>芸術家</t>
+        </is>
+      </c>
+      <c r="D524" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E524" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B525" s="5" t="inlineStr">
+        <is>
+          <t>writer</t>
+        </is>
+      </c>
+      <c r="C525" s="5" t="inlineStr">
+        <is>
+          <t>作家</t>
+        </is>
+      </c>
+      <c r="D525" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E525" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B526" s="5" t="inlineStr">
+        <is>
+          <t>singer</t>
+        </is>
+      </c>
+      <c r="C526" s="5" t="inlineStr">
+        <is>
+          <t>歌手</t>
+        </is>
+      </c>
+      <c r="D526" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E526" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B527" s="5" t="inlineStr">
+        <is>
+          <t>comedian</t>
+        </is>
+      </c>
+      <c r="C527" s="5" t="inlineStr">
+        <is>
+          <t>お笑い芸人</t>
+        </is>
+      </c>
+      <c r="D527" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E527" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B528" s="5" t="inlineStr">
+        <is>
+          <t>doctor</t>
+        </is>
+      </c>
+      <c r="C528" s="5" t="inlineStr">
+        <is>
+          <t>医者</t>
+        </is>
+      </c>
+      <c r="D528" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E528" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B529" s="5" t="inlineStr">
+        <is>
+          <t>nurse</t>
+        </is>
+      </c>
+      <c r="C529" s="5" t="inlineStr">
+        <is>
+          <t>看護師</t>
+        </is>
+      </c>
+      <c r="D529" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E529" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B530" s="5" t="inlineStr">
+        <is>
+          <t>vet</t>
+        </is>
+      </c>
+      <c r="C530" s="5" t="inlineStr">
+        <is>
+          <t>獣医</t>
+        </is>
+      </c>
+      <c r="D530" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E530" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B531" s="5" t="inlineStr">
+        <is>
+          <t>zookeeper</t>
+        </is>
+      </c>
+      <c r="C531" s="5" t="inlineStr">
+        <is>
+          <t>飼育員</t>
+        </is>
+      </c>
+      <c r="D531" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E531" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B532" s="5" t="inlineStr">
+        <is>
+          <t>cook</t>
+        </is>
+      </c>
+      <c r="C532" s="5" t="inlineStr">
+        <is>
+          <t>料理人</t>
+        </is>
+      </c>
+      <c r="D532" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E532" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B533" s="5" t="inlineStr">
+        <is>
+          <t>baker</t>
+        </is>
+      </c>
+      <c r="C533" s="5" t="inlineStr">
+        <is>
+          <t>パン職人</t>
+        </is>
+      </c>
+      <c r="D533" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E533" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B534" s="5" t="inlineStr">
+        <is>
+          <t>farmer</t>
+        </is>
+      </c>
+      <c r="C534" s="5" t="inlineStr">
+        <is>
+          <t>農家</t>
+        </is>
+      </c>
+      <c r="D534" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E534" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B535" s="5" t="inlineStr">
+        <is>
+          <t>police officer</t>
+        </is>
+      </c>
+      <c r="C535" s="5" t="inlineStr">
+        <is>
+          <t>警察官</t>
+        </is>
+      </c>
+      <c r="D535" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E535" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B536" s="5" t="inlineStr">
+        <is>
+          <t>fire fighter</t>
+        </is>
+      </c>
+      <c r="C536" s="5" t="inlineStr">
+        <is>
+          <t>消防士</t>
+        </is>
+      </c>
+      <c r="D536" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E536" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B537" s="5" t="inlineStr">
+        <is>
+          <t>pilot</t>
+        </is>
+      </c>
+      <c r="C537" s="5" t="inlineStr">
+        <is>
+          <t>パイロット</t>
+        </is>
+      </c>
+      <c r="D537" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E537" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B538" s="5" t="inlineStr">
+        <is>
+          <t>programmer</t>
+        </is>
+      </c>
+      <c r="C538" s="5" t="inlineStr">
+        <is>
+          <t>プログラマー</t>
+        </is>
+      </c>
+      <c r="D538" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E538" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B539" s="5" t="inlineStr">
+        <is>
+          <t>office worker</t>
+        </is>
+      </c>
+      <c r="C539" s="5" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="D539" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E539" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B540" s="5" t="inlineStr">
+        <is>
+          <t>astronaut</t>
+        </is>
+      </c>
+      <c r="C540" s="5" t="inlineStr">
+        <is>
+          <t>宇宙飛行士</t>
+        </is>
+      </c>
+      <c r="D540" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E540" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B541" s="5" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="C541" s="5" t="inlineStr">
+        <is>
+          <t>先生</t>
+        </is>
+      </c>
+      <c r="D541" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E541" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B542" s="5" t="inlineStr">
+        <is>
+          <t>researcher</t>
+        </is>
+      </c>
+      <c r="C542" s="5" t="inlineStr">
+        <is>
+          <t>研究者</t>
+        </is>
+      </c>
+      <c r="D542" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E542" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B543" s="5" t="inlineStr">
+        <is>
+          <t>scientist</t>
+        </is>
+      </c>
+      <c r="C543" s="5" t="inlineStr">
+        <is>
+          <t>科学者</t>
+        </is>
+      </c>
+      <c r="D543" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E543" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B544" s="5" t="inlineStr">
+        <is>
+          <t>flight attendant</t>
+        </is>
+      </c>
+      <c r="C544" s="5" t="inlineStr">
+        <is>
+          <t>客室乗務員</t>
+        </is>
+      </c>
+      <c r="D544" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E544" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B545" s="5" t="inlineStr">
+        <is>
+          <t>baseball player</t>
+        </is>
+      </c>
+      <c r="C545" s="5" t="inlineStr">
+        <is>
+          <t>野球選手</t>
+        </is>
+      </c>
+      <c r="D545" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E545" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B546" s="5" t="inlineStr">
+        <is>
+          <t>mountaineer</t>
+        </is>
+      </c>
+      <c r="C546" s="5" t="inlineStr">
+        <is>
+          <t>登山家</t>
+        </is>
+      </c>
+      <c r="D546" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="E546" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B547" s="5" t="inlineStr">
+        <is>
+          <t>baseball team</t>
+        </is>
+      </c>
+      <c r="C547" s="5" t="inlineStr">
+        <is>
+          <t>野球部</t>
+        </is>
+      </c>
+      <c r="D547" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E547" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B548" s="5" t="inlineStr">
+        <is>
+          <t>softball team</t>
+        </is>
+      </c>
+      <c r="C548" s="5" t="inlineStr">
+        <is>
+          <t>ソフトボール部</t>
+        </is>
+      </c>
+      <c r="D548" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E548" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B549" s="5" t="inlineStr">
+        <is>
+          <t>basketball team</t>
+        </is>
+      </c>
+      <c r="C549" s="5" t="inlineStr">
+        <is>
+          <t>バスケ部</t>
+        </is>
+      </c>
+      <c r="D549" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E549" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B550" s="5" t="inlineStr">
+        <is>
+          <t>volleyball team</t>
+        </is>
+      </c>
+      <c r="C550" s="5" t="inlineStr">
+        <is>
+          <t>バレー部</t>
+        </is>
+      </c>
+      <c r="D550" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E550" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B551" s="5" t="inlineStr">
+        <is>
+          <t>soccer team</t>
+        </is>
+      </c>
+      <c r="C551" s="5" t="inlineStr">
+        <is>
+          <t>サッカー部</t>
+        </is>
+      </c>
+      <c r="D551" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E551" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B552" s="5" t="inlineStr">
+        <is>
+          <t>tennis team</t>
+        </is>
+      </c>
+      <c r="C552" s="5" t="inlineStr">
+        <is>
+          <t>テニス部</t>
+        </is>
+      </c>
+      <c r="D552" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E552" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B553" s="5" t="inlineStr">
+        <is>
+          <t>table tennis team</t>
+        </is>
+      </c>
+      <c r="C553" s="5" t="inlineStr">
+        <is>
+          <t>卓球部</t>
+        </is>
+      </c>
+      <c r="D553" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E553" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B554" s="5" t="inlineStr">
+        <is>
+          <t>badminton team</t>
+        </is>
+      </c>
+      <c r="C554" s="5" t="inlineStr">
+        <is>
+          <t>バドミントン部</t>
+        </is>
+      </c>
+      <c r="D554" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E554" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B555" s="5" t="inlineStr">
+        <is>
+          <t>dance team</t>
+        </is>
+      </c>
+      <c r="C555" s="5" t="inlineStr">
+        <is>
+          <t>ダンス部</t>
+        </is>
+      </c>
+      <c r="D555" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E555" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B556" s="5" t="inlineStr">
+        <is>
+          <t>track and field team</t>
+        </is>
+      </c>
+      <c r="C556" s="5" t="inlineStr">
+        <is>
+          <t>陸上部</t>
+        </is>
+      </c>
+      <c r="D556" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E556" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B557" s="5" t="inlineStr">
+        <is>
+          <t>art club</t>
+        </is>
+      </c>
+      <c r="C557" s="5" t="inlineStr">
+        <is>
+          <t>美術部</t>
+        </is>
+      </c>
+      <c r="D557" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E557" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B558" s="5" t="inlineStr">
+        <is>
+          <t>cooking club</t>
+        </is>
+      </c>
+      <c r="C558" s="5" t="inlineStr">
+        <is>
+          <t>料理部</t>
+        </is>
+      </c>
+      <c r="D558" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E558" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B559" s="5" t="inlineStr">
+        <is>
+          <t>drama club</t>
+        </is>
+      </c>
+      <c r="C559" s="5" t="inlineStr">
+        <is>
+          <t>演劇部</t>
+        </is>
+      </c>
+      <c r="D559" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E559" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B560" s="5" t="inlineStr">
+        <is>
+          <t>brass band</t>
+        </is>
+      </c>
+      <c r="C560" s="5" t="inlineStr">
+        <is>
+          <t>吹奏楽部</t>
+        </is>
+      </c>
+      <c r="D560" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E560" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B561" s="5" t="inlineStr">
+        <is>
+          <t>chorus</t>
+        </is>
+      </c>
+      <c r="C561" s="5" t="inlineStr">
+        <is>
+          <t>合唱部</t>
+        </is>
+      </c>
+      <c r="D561" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E561" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B562" s="5" t="inlineStr">
+        <is>
+          <t>broadcasting club</t>
+        </is>
+      </c>
+      <c r="C562" s="5" t="inlineStr">
+        <is>
+          <t>放送部</t>
+        </is>
+      </c>
+      <c r="D562" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E562" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B563" s="5" t="inlineStr">
+        <is>
+          <t>newspaper club</t>
+        </is>
+      </c>
+      <c r="C563" s="5" t="inlineStr">
+        <is>
+          <t>新聞部</t>
+        </is>
+      </c>
+      <c r="D563" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E563" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B564" s="5" t="inlineStr">
+        <is>
+          <t>photography club</t>
+        </is>
+      </c>
+      <c r="C564" s="5" t="inlineStr">
+        <is>
+          <t>写真部</t>
+        </is>
+      </c>
+      <c r="D564" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="E564" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E263"/>
+  <autoFilter ref="A1:E564"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7183,7 +14708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7491,6 +15016,336 @@
       </c>
       <c r="C20" s="5" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>スポーツ</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>動物</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>自然</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>海の生き物</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>虫</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>性格</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>He is ◯◯.</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>This is ◯◯.</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>一日の生活</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>I ◯◯.</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>衣類</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>This is my ◯◯.</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>文房具</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>楽器</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>I can play the ◯◯.</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>身の回りのもの</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>I want a new ◯◯.</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>遊びなど</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>学校行事</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>I like the ◯◯.</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>年中行事</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>I like ◯◯.</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>感想・様子</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>It's ◯◯.</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>I want to be ◯◯.</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>部活動</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>I want to join the ◯◯.</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
